--- a/data/poi_evaluation_metrics.xlsx
+++ b/data/poi_evaluation_metrics.xlsx
@@ -479,19 +479,19 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9992454717864121</v>
+        <v>0.9998338943534336</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004604581558650857</v>
+        <v>0.004600345025876941</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fuzzy_ahp</t>
+          <t>crisp_ahp_weighted_baseline</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -507,19 +507,19 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9988906871791947</v>
+        <v>0.9984687146681125</v>
       </c>
       <c r="G3" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004604581558650857</v>
+        <v>0.004600345025876941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>crisp_ahp_weighted_baseline</t>
+          <t>fuzzy_ahp</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -535,26 +535,26 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9988146130163909</v>
+        <v>0.9979889195015115</v>
       </c>
       <c r="G4" t="n">
-        <v>0.45</v>
+        <v>0.425</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004604581558650857</v>
+        <v>0.004600345025876941</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>type_location_baseline</t>
+          <t>distance_baseline</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02298850574712644</v>
+        <v>0.02241379310344828</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -563,41 +563,41 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9549964109109786</v>
+        <v>0.9744743058658987</v>
       </c>
       <c r="G5" t="n">
-        <v>0.425</v>
+        <v>0.725</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004604581558650857</v>
+        <v>0.004600345025876941</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>distance_baseline</t>
+          <t>type_location_baseline</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02011494252873563</v>
+        <v>0.02298850574712644</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9119047619047619</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9241648035765788</v>
+        <v>0.9683083494496989</v>
       </c>
       <c r="G6" t="n">
-        <v>0.425</v>
+        <v>0.4</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004604581558650857</v>
+        <v>0.004600345025876941</v>
       </c>
     </row>
     <row r="7">
@@ -607,25 +607,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.425</v>
+        <v>0.525</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009770114942528735</v>
+        <v>0.01206896551724138</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6731150793650793</v>
+        <v>0.5324700018896448</v>
       </c>
       <c r="E7" t="n">
         <v>0.75</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6905653543664456</v>
+        <v>0.6323740640849521</v>
       </c>
       <c r="G7" t="n">
         <v>0.8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001151145389662714</v>
+        <v>0.001150086256469235</v>
       </c>
     </row>
     <row r="8">
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="C8" t="n">
-        <v>0.006896551724137931</v>
+        <v>0.005747126436781609</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3995181405895691</v>
+        <v>0.3785383597883598</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4955527789682926</v>
+        <v>0.5201980082979515</v>
       </c>
       <c r="G8" t="n">
         <v>0.325</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003798779785886957</v>
+        <v>0.003795284646348476</v>
       </c>
     </row>
   </sheetData>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01379310344827586</v>
+        <v>0.01839080459770115</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9150793650793649</v>
+        <v>0.8385912698412699</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.973875295847043</v>
+        <v>0.9442700594997422</v>
       </c>
       <c r="H2" t="n">
         <v>0.8</v>
@@ -766,10 +766,10 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9548382310698215</v>
+        <v>0.9546869932228652</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006896551724137931</v>
+        <v>0.009195402298850575</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7678571428571428</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9222258765926029</v>
+        <v>0.9056667090537307</v>
       </c>
       <c r="H4" t="n">
         <v>0.4</v>
@@ -826,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9329610352113484</v>
+        <v>0.9587643753671373</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9981488429155477</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -886,10 +886,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.999994959433932</v>
+        <v>0.9995097431707665</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9998632188719916</v>
+        <v>0.9993173077656277</v>
       </c>
       <c r="H8" t="n">
         <v>0.5</v>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01609195402298851</v>
+        <v>0.01379310344827586</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8273809523809524</v>
+        <v>0.6537037037037037</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8316618117451827</v>
+        <v>0.7638101330756178</v>
       </c>
       <c r="H9" t="n">
         <v>0.8</v>
@@ -976,10 +976,10 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9501470784085747</v>
+        <v>0.9644124791992723</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004597701149425287</v>
+        <v>0.006896551724137931</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.5074074074074074</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1111111111111111</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3609221094260708</v>
+        <v>0.7264625536608735</v>
       </c>
       <c r="H11" t="n">
         <v>0.4</v>
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9580769540504976</v>
+        <v>0.9862337963487378</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
@@ -1066,10 +1066,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9997969127962875</v>
+        <v>0.9997715926780687</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -1096,10 +1096,10 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9967910412104176</v>
+        <v>0.9996122438882833</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
@@ -1126,10 +1126,10 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9964027814427207</v>
+        <v>0.9995477986063926</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -1174,22 +1174,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01149425287356322</v>
+        <v>0.02068965517241379</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6476190476190476</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8005808556899952</v>
+        <v>0.9868419048839047</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18">
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9478363395743855</v>
+        <v>0.9569228019423474</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9997602213225241</v>
+        <v>0.9999830467723543</v>
       </c>
       <c r="H20" t="n">
         <v>0.3</v>
@@ -1306,7 +1306,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9999791209401727</v>
+        <v>0.9999893717488948</v>
       </c>
       <c r="H21" t="n">
         <v>0.3</v>
@@ -1336,10 +1336,10 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9998900636969851</v>
+        <v>0.9999564979925134</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23">
@@ -1354,19 +1354,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="D23" t="n">
-        <v>0.009195402298850575</v>
+        <v>0.01609195402298851</v>
       </c>
       <c r="E23" t="n">
-        <v>0.95</v>
+        <v>0.6375850340136054</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9567243098735569</v>
+        <v>0.8214160637644485</v>
       </c>
       <c r="H23" t="n">
         <v>0.8</v>
@@ -1396,10 +1396,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9910930491379238</v>
+        <v>0.9919558461575523</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25">
@@ -1414,19 +1414,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01609195402298851</v>
+        <v>0.006896551724137931</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6091836734693877</v>
+        <v>0.2388888888888888</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6990631298544968</v>
+        <v>0.4486627704772018</v>
       </c>
       <c r="H25" t="n">
         <v>0.2</v>
@@ -1456,10 +1456,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.981111314807683</v>
+        <v>0.9713124241405731</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27">
@@ -1486,10 +1486,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9992759101112889</v>
+        <v>0.9995809379633114</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="28">
@@ -1516,7 +1516,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9984933304810412</v>
+        <v>0.9947634998645053</v>
       </c>
       <c r="H28" t="n">
         <v>0.3</v>
@@ -1546,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9994066847050814</v>
+        <v>0.9931340736415124</v>
       </c>
       <c r="H29" t="n">
         <v>0.3</v>
@@ -1601,7 +1601,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>behavior</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1623,7 +1623,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>content</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1645,7 +1645,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>distance</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1667,7 +1667,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>distance</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1689,7 +1689,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>context</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/data/poi_evaluation_metrics.xlsx
+++ b/data/poi_evaluation_metrics.xlsx
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,42 +431,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precision@10</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>recall@10</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>map@10</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>mrr@10</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ndcg@10</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>type_diversity@10</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>catalog_coverage@10</t>
         </is>
@@ -479,10 +491,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9998338943534336</v>
+        <v>0.9997992022567738</v>
       </c>
       <c r="G2" t="n">
-        <v>0.35</v>
+        <v>0.325</v>
       </c>
       <c r="H2" t="n">
         <v>0.004600345025876941</v>
@@ -507,10 +519,10 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9984687146681125</v>
+        <v>0.9991988362944211</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H3" t="n">
         <v>0.004600345025876941</v>
@@ -535,10 +547,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9979889195015115</v>
+        <v>0.9978593433343224</v>
       </c>
       <c r="G4" t="n">
-        <v>0.425</v>
+        <v>0.35</v>
       </c>
       <c r="H4" t="n">
         <v>0.004600345025876941</v>
@@ -563,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9744743058658987</v>
+        <v>0.9720097889813782</v>
       </c>
       <c r="G5" t="n">
         <v>0.725</v>
@@ -591,7 +603,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9683083494496989</v>
+        <v>0.9684971993930528</v>
       </c>
       <c r="G6" t="n">
         <v>0.4</v>
@@ -607,19 +619,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.525</v>
+        <v>0.4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01206896551724138</v>
+        <v>0.009195402298850575</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5324700018896448</v>
+        <v>0.4873327664399093</v>
       </c>
       <c r="E7" t="n">
         <v>0.75</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6323740640849521</v>
+        <v>0.6089117992109014</v>
       </c>
       <c r="G7" t="n">
         <v>0.8</v>
@@ -635,19 +647,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.25</v>
+        <v>0.225</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005747126436781609</v>
+        <v>0.005172413793103448</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3785383597883598</v>
+        <v>0.2917328042328042</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5201980082979515</v>
+        <v>0.4462179042738293</v>
       </c>
       <c r="G8" t="n">
         <v>0.325</v>
@@ -671,42 +683,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>profile</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precision@10</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>recall@10</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>map@10</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mrr@10</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ndcg@10</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>type_diversity@10</t>
         </is>
@@ -724,19 +736,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01839080459770115</v>
+        <v>0.009195402298850575</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8385912698412699</v>
+        <v>0.7678571428571428</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9442700594997422</v>
+        <v>0.9081404716688291</v>
       </c>
       <c r="H2" t="n">
         <v>0.8</v>
@@ -766,7 +778,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9546869932228652</v>
+        <v>0.9549779965945587</v>
       </c>
       <c r="H3" t="n">
         <v>0.9</v>
@@ -784,19 +796,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009195402298850575</v>
+        <v>0.006896551724137931</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7678571428571428</v>
+        <v>0.4206349206349206</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9056667090537307</v>
+        <v>0.6200766549081679</v>
       </c>
       <c r="H4" t="n">
         <v>0.4</v>
@@ -826,10 +838,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9587643753671373</v>
+        <v>0.9849670240058352</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -886,10 +898,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9995097431707665</v>
+        <v>0.9998159654448776</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -916,10 +928,10 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9993173077656277</v>
+        <v>0.9997647051026394</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
@@ -934,19 +946,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01379310344827586</v>
+        <v>0.01149425287356322</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6537037037037037</v>
+        <v>0.5438888888888889</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7638101330756178</v>
+        <v>0.7063373409845971</v>
       </c>
       <c r="H9" t="n">
         <v>0.8</v>
@@ -976,7 +988,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9644124791992723</v>
+        <v>0.9587845950408586</v>
       </c>
       <c r="H10" t="n">
         <v>0.8</v>
@@ -1006,7 +1018,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7264625536608735</v>
+        <v>0.7157056659679879</v>
       </c>
       <c r="H11" t="n">
         <v>0.4</v>
@@ -1036,10 +1048,10 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9862337963487378</v>
+        <v>0.9509010149916496</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -1186,7 +1198,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9868419048839047</v>
+        <v>0.9861213107186256</v>
       </c>
       <c r="H17" t="n">
         <v>0.6</v>
@@ -1246,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9569228019423474</v>
+        <v>0.9809983185399556</v>
       </c>
       <c r="H19" t="n">
         <v>0.5</v>
@@ -1366,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8214160637644485</v>
+        <v>0.8211693841901796</v>
       </c>
       <c r="H23" t="n">
         <v>0.8</v>
@@ -1396,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9919558461575523</v>
+        <v>0.9881552535714699</v>
       </c>
       <c r="H24" t="n">
         <v>0.6</v>
@@ -1426,7 +1438,7 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4486627704772018</v>
+        <v>0.4490892962191613</v>
       </c>
       <c r="H25" t="n">
         <v>0.2</v>
@@ -1456,7 +1468,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9713124241405731</v>
+        <v>0.9571224400347708</v>
       </c>
       <c r="H26" t="n">
         <v>0.2</v>
@@ -1486,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9995809379633114</v>
+        <v>0.9994421695766722</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -1516,10 +1528,10 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9947634998645053</v>
+        <v>0.9973777640956285</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
@@ -1546,10 +1558,10 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9931340736415124</v>
+        <v>0.9921683716357439</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1567,32 +1579,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>criterion</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ahp_weight_from_pairwise</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>fuzzy_weight_l</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>fuzzy_weight_m</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fuzzy_weight_u</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>defuzzified_weight</t>
         </is>
